--- a/checklist_forms/002_healthy_relationship_checklist--checklist_forms.xlsx
+++ b/checklist_forms/002_healthy_relationship_checklist--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,59 +548,63 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>communication</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>How do you communicate with your partner?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please describe your communication style</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>conflict_resolution</t>
+          <t>intimacy_level</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Conflict Resolution</t>
+          <t>What is your level of physical intimacy?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>intimacy_level</t>
+          <t>conflict_resolution</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Intimacy Level</t>
+          <t>How do you resolve conflicts?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,30 +621,30 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Emotional Maturity</t>
+          <t>What is your partner's emotional maturity level?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>conflict_resolution</t>
+          <t>conflict_resolution_options</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Conflict Resolution</t>
+          <t>What are some strategies you use to resolve conflicts?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,115 +657,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>conflict_resolution_options</t>
+          <t>relationship_strength</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Conflict Resolution Options</t>
+          <t>What is the strength of your relationship?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>emotional_maturity</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Emotional Maturity</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>intimacy_level</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Intimacy Level</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>conflict_resolution</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Conflict Resolution</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>communication</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Communication</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -776,12 +688,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +721,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>partnership</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Partnership</t>
         </is>
       </c>
     </row>
@@ -826,29 +738,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>friendship</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Friendship</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>conflict_resolution_choices</t>
+          <t>relationship_survey_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>family_members</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Family Members</t>
         </is>
       </c>
     </row>
@@ -860,12 +772,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -877,12 +789,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -894,46 +806,63 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>conflict_resolution_choices</t>
+          <t>relationship_strength_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>conflict_resolution_choices</t>
+          <t>relationship_strength_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>relationship_strength_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Weak</t>
         </is>
       </c>
     </row>
